--- a/input/12cut_non_AB.xlsx
+++ b/input/12cut_non_AB.xlsx
@@ -1804,6 +1804,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,30 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1843,11 +1849,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1858,11 +1864,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,40 +1942,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
@@ -1954,145 +1969,136 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
@@ -2101,73 +2107,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2633,7 +2633,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="343" t="inlineStr">
+      <c r="A1" s="325" t="inlineStr">
         <is>
           <t>12 граней холодная фиксация с эффектом АВ</t>
         </is>
@@ -2695,26 +2695,26 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A3" s="311" t="inlineStr">
+      <c r="A3" s="313" t="inlineStr">
         <is>
           <t>Jet Black AB</t>
         </is>
       </c>
-      <c r="B3" s="303" t="inlineStr">
+      <c r="B3" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C3" s="311" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D3" s="311" t="n">
+      <c r="C3" s="313" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D3" s="313" t="n">
         <v>195</v>
       </c>
-      <c r="E3" s="311" t="n">
+      <c r="E3" s="313" t="n">
         <v>50</v>
       </c>
-      <c r="F3" s="311" t="n"/>
+      <c r="F3" s="313" t="n"/>
       <c r="G3" s="263">
         <f>E3-F3</f>
         <v/>
@@ -2732,22 +2732,22 @@
     </row>
     <row r="4">
       <c r="A4" s="429" t="n"/>
-      <c r="B4" s="301" t="inlineStr">
+      <c r="B4" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C4" s="312" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D4" s="312" t="n">
+      <c r="C4" s="314" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D4" s="314" t="n">
         <v>240</v>
       </c>
-      <c r="E4" s="312">
+      <c r="E4" s="314">
         <f>8+40</f>
         <v/>
       </c>
-      <c r="F4" s="312" t="n"/>
+      <c r="F4" s="314" t="n"/>
       <c r="G4" s="264">
         <f>E4-F4</f>
         <v/>
@@ -2761,22 +2761,22 @@
     </row>
     <row r="5">
       <c r="A5" s="429" t="n"/>
-      <c r="B5" s="301" t="inlineStr">
+      <c r="B5" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C5" s="312" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D5" s="312" t="n">
+      <c r="C5" s="314" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D5" s="314" t="n">
         <v>262</v>
       </c>
-      <c r="E5" s="312">
+      <c r="E5" s="314">
         <f>15+35</f>
         <v/>
       </c>
-      <c r="F5" s="312" t="n"/>
+      <c r="F5" s="314" t="n"/>
       <c r="G5" s="264">
         <f>E5-F5</f>
         <v/>
@@ -2790,22 +2790,22 @@
     </row>
     <row r="6">
       <c r="A6" s="429" t="n"/>
-      <c r="B6" s="301" t="inlineStr">
+      <c r="B6" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C6" s="312" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D6" s="312" t="n">
+      <c r="C6" s="314" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D6" s="314" t="n">
         <v>370</v>
       </c>
-      <c r="E6" s="312">
+      <c r="E6" s="314">
         <f>20+30</f>
         <v/>
       </c>
-      <c r="F6" s="312" t="n">
+      <c r="F6" s="314" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="264">
@@ -2821,22 +2821,22 @@
     </row>
     <row r="7">
       <c r="A7" s="429" t="n"/>
-      <c r="B7" s="301" t="inlineStr">
+      <c r="B7" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C7" s="312" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D7" s="312" t="n">
+      <c r="C7" s="314" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D7" s="314" t="n">
         <v>485</v>
       </c>
-      <c r="E7" s="312">
+      <c r="E7" s="314">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F7" s="312" t="n"/>
+      <c r="F7" s="314" t="n"/>
       <c r="G7" s="264">
         <f>E7-F7</f>
         <v/>
@@ -2850,22 +2850,22 @@
     </row>
     <row r="8">
       <c r="A8" s="429" t="n"/>
-      <c r="B8" s="301" t="inlineStr">
+      <c r="B8" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C8" s="312" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D8" s="312" t="n">
+      <c r="C8" s="314" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D8" s="314" t="n">
         <v>693</v>
       </c>
-      <c r="E8" s="312">
+      <c r="E8" s="314">
         <f>3*15+4</f>
         <v/>
       </c>
-      <c r="F8" s="312" t="n"/>
+      <c r="F8" s="314" t="n"/>
       <c r="G8" s="264">
         <f>E8-F8</f>
         <v/>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="431" t="n"/>
-      <c r="B9" s="302" t="inlineStr">
+      <c r="B9" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C9" s="313" t="n">
+      <c r="C9" s="315" t="n">
         <v>288</v>
       </c>
-      <c r="D9" s="313" t="n">
+      <c r="D9" s="315" t="n">
         <v>455</v>
       </c>
-      <c r="E9" s="313">
+      <c r="E9" s="315">
         <f>25+23</f>
         <v/>
       </c>
-      <c r="F9" s="313" t="n"/>
+      <c r="F9" s="315" t="n"/>
       <c r="G9" s="265">
         <f>E9-F9</f>
         <v/>
@@ -2907,26 +2907,26 @@
       <c r="I9" s="274" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A10" s="311" t="inlineStr">
+      <c r="A10" s="313" t="inlineStr">
         <is>
           <t>Smoked Topaz AB</t>
         </is>
       </c>
-      <c r="B10" s="303" t="inlineStr">
+      <c r="B10" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C10" s="311" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D10" s="311" t="n">
+      <c r="C10" s="313" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D10" s="313" t="n">
         <v>499</v>
       </c>
-      <c r="E10" s="311" t="n">
+      <c r="E10" s="313" t="n">
         <v>20</v>
       </c>
-      <c r="F10" s="311" t="n"/>
+      <c r="F10" s="313" t="n"/>
       <c r="G10" s="263">
         <f>E10-F10</f>
         <v/>
@@ -2944,22 +2944,22 @@
     </row>
     <row r="11">
       <c r="A11" s="429" t="n"/>
-      <c r="B11" s="301" t="inlineStr">
+      <c r="B11" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C11" s="312" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D11" s="312" t="n">
+      <c r="C11" s="314" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D11" s="314" t="n">
         <v>803</v>
       </c>
-      <c r="E11" s="312">
+      <c r="E11" s="314">
         <f>15+2</f>
         <v/>
       </c>
-      <c r="F11" s="312" t="n"/>
+      <c r="F11" s="314" t="n"/>
       <c r="G11" s="264">
         <f>E11-F11</f>
         <v/>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="A12" s="431" t="n"/>
-      <c r="B12" s="302" t="inlineStr">
+      <c r="B12" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C12" s="313" t="n">
+      <c r="C12" s="315" t="n">
         <v>288</v>
       </c>
-      <c r="D12" s="313" t="n">
+      <c r="D12" s="315" t="n">
         <v>478</v>
       </c>
-      <c r="E12" s="313">
+      <c r="E12" s="315">
         <f>19</f>
         <v/>
       </c>
-      <c r="F12" s="313" t="n"/>
+      <c r="F12" s="315" t="n"/>
       <c r="G12" s="265">
         <f>E12-F12</f>
         <v/>
@@ -3001,26 +3001,26 @@
       <c r="I12" s="274" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A13" s="303" t="inlineStr">
+      <c r="A13" s="310" t="inlineStr">
         <is>
           <t>Lt.Colorado Topaz AB</t>
         </is>
       </c>
-      <c r="B13" s="303" t="inlineStr">
+      <c r="B13" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C13" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D13" s="303" t="n">
+      <c r="C13" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D13" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E13" s="303" t="n">
+      <c r="E13" s="310" t="n">
         <v>50</v>
       </c>
-      <c r="F13" s="311" t="n"/>
+      <c r="F13" s="313" t="n"/>
       <c r="G13" s="263">
         <f>E13-F13</f>
         <v/>
@@ -3038,21 +3038,21 @@
     </row>
     <row r="14">
       <c r="A14" s="429" t="n"/>
-      <c r="B14" s="301" t="inlineStr">
+      <c r="B14" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C14" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D14" s="301" t="n">
+      <c r="C14" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D14" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E14" s="301" t="n">
+      <c r="E14" s="311" t="n">
         <v>40</v>
       </c>
-      <c r="F14" s="312" t="n"/>
+      <c r="F14" s="314" t="n"/>
       <c r="G14" s="264">
         <f>E14-F14</f>
         <v/>
@@ -3066,22 +3066,22 @@
     </row>
     <row r="15">
       <c r="A15" s="429" t="n"/>
-      <c r="B15" s="301" t="inlineStr">
+      <c r="B15" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C15" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D15" s="301" t="n">
+      <c r="C15" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D15" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E15" s="301">
+      <c r="E15" s="311">
         <f>35+14</f>
         <v/>
       </c>
-      <c r="F15" s="312" t="n"/>
+      <c r="F15" s="314" t="n"/>
       <c r="G15" s="264">
         <f>E15-F15</f>
         <v/>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="16">
       <c r="A16" s="429" t="n"/>
-      <c r="B16" s="301" t="inlineStr">
+      <c r="B16" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C16" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D16" s="301" t="n">
+      <c r="C16" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D16" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E16" s="301">
+      <c r="E16" s="311">
         <f>19+30</f>
         <v/>
       </c>
-      <c r="F16" s="312" t="n">
+      <c r="F16" s="314" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="264">
@@ -3126,22 +3126,22 @@
     </row>
     <row r="17">
       <c r="A17" s="429" t="n"/>
-      <c r="B17" s="301" t="inlineStr">
+      <c r="B17" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C17" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D17" s="301" t="n">
+      <c r="C17" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D17" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E17" s="301">
+      <c r="E17" s="311">
         <f>24+25</f>
         <v/>
       </c>
-      <c r="F17" s="312">
+      <c r="F17" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -3158,22 +3158,22 @@
     </row>
     <row r="18">
       <c r="A18" s="429" t="n"/>
-      <c r="B18" s="301" t="inlineStr">
+      <c r="B18" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C18" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D18" s="301" t="n">
+      <c r="C18" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D18" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E18" s="301">
+      <c r="E18" s="311">
         <f>3*15+1</f>
         <v/>
       </c>
-      <c r="F18" s="312">
+      <c r="F18" s="314">
         <f>10+1+1+1+1</f>
         <v/>
       </c>
@@ -3190,22 +3190,22 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" thickBot="1">
       <c r="A19" s="431" t="n"/>
-      <c r="B19" s="302" t="inlineStr">
+      <c r="B19" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C19" s="302" t="n">
+      <c r="C19" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D19" s="302" t="n">
+      <c r="D19" s="312" t="n">
         <v>478</v>
       </c>
-      <c r="E19" s="302">
+      <c r="E19" s="312">
         <f>25+23</f>
         <v/>
       </c>
-      <c r="F19" s="313">
+      <c r="F19" s="315">
         <f>1+6</f>
         <v/>
       </c>
@@ -3221,26 +3221,26 @@
       <c r="I19" s="274" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A20" s="303" t="inlineStr">
+      <c r="A20" s="310" t="inlineStr">
         <is>
           <t>Sapphire AB</t>
         </is>
       </c>
-      <c r="B20" s="303" t="inlineStr">
+      <c r="B20" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C20" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D20" s="303" t="n">
+      <c r="C20" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D20" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E20" s="303" t="n">
+      <c r="E20" s="310" t="n">
         <v>48</v>
       </c>
-      <c r="F20" s="311" t="n"/>
+      <c r="F20" s="313" t="n"/>
       <c r="G20" s="263">
         <f>E20-F20</f>
         <v/>
@@ -3258,21 +3258,21 @@
     </row>
     <row r="21">
       <c r="A21" s="429" t="n"/>
-      <c r="B21" s="301" t="inlineStr">
+      <c r="B21" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C21" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D21" s="301" t="n">
+      <c r="C21" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D21" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E21" s="301" t="n">
+      <c r="E21" s="311" t="n">
         <v>40</v>
       </c>
-      <c r="F21" s="312" t="n"/>
+      <c r="F21" s="314" t="n"/>
       <c r="G21" s="264">
         <f>E21-F21</f>
         <v/>
@@ -3286,21 +3286,21 @@
     </row>
     <row r="22">
       <c r="A22" s="429" t="n"/>
-      <c r="B22" s="301" t="inlineStr">
+      <c r="B22" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C22" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D22" s="301" t="n">
+      <c r="C22" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D22" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E22" s="301" t="n">
+      <c r="E22" s="311" t="n">
         <v>49</v>
       </c>
-      <c r="F22" s="312" t="n"/>
+      <c r="F22" s="314" t="n"/>
       <c r="G22" s="264">
         <f>E22-F22</f>
         <v/>
@@ -3314,21 +3314,21 @@
     </row>
     <row r="23">
       <c r="A23" s="429" t="n"/>
-      <c r="B23" s="301" t="inlineStr">
+      <c r="B23" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C23" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D23" s="301" t="n">
+      <c r="C23" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D23" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E23" s="301" t="n">
+      <c r="E23" s="311" t="n">
         <v>50</v>
       </c>
-      <c r="F23" s="312">
+      <c r="F23" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -3345,21 +3345,21 @@
     </row>
     <row r="24">
       <c r="A24" s="429" t="n"/>
-      <c r="B24" s="301" t="inlineStr">
+      <c r="B24" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C24" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D24" s="301" t="n">
+      <c r="C24" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D24" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E24" s="301" t="n">
+      <c r="E24" s="311" t="n">
         <v>49</v>
       </c>
-      <c r="F24" s="312">
+      <c r="F24" s="314">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -3376,22 +3376,22 @@
     </row>
     <row r="25">
       <c r="A25" s="429" t="n"/>
-      <c r="B25" s="301" t="inlineStr">
+      <c r="B25" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C25" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D25" s="301" t="n">
+      <c r="C25" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D25" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E25" s="301">
+      <c r="E25" s="311">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F25" s="312">
+      <c r="F25" s="314">
         <f>6+1+1+1+1</f>
         <v/>
       </c>
@@ -3408,22 +3408,22 @@
     </row>
     <row r="26">
       <c r="A26" s="429" t="n"/>
-      <c r="B26" s="301" t="inlineStr">
+      <c r="B26" s="311" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C26" s="301" t="n">
+      <c r="C26" s="311" t="n">
         <v>288</v>
       </c>
-      <c r="D26" s="301" t="n">
+      <c r="D26" s="311" t="n">
         <v>478</v>
       </c>
-      <c r="E26" s="301">
+      <c r="E26" s="311">
         <f>25+22</f>
         <v/>
       </c>
-      <c r="F26" s="312">
+      <c r="F26" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -3440,22 +3440,22 @@
     </row>
     <row r="27" ht="15.75" customHeight="1" thickBot="1">
       <c r="A27" s="431" t="n"/>
-      <c r="B27" s="339" t="inlineStr">
+      <c r="B27" s="331" t="inlineStr">
         <is>
           <t>SS34</t>
         </is>
       </c>
-      <c r="C27" s="302" t="n">
+      <c r="C27" s="312" t="n">
         <v>144</v>
       </c>
-      <c r="D27" s="302" t="n">
+      <c r="D27" s="312" t="n">
         <v>800</v>
       </c>
-      <c r="E27" s="302">
+      <c r="E27" s="312">
         <f>3*25</f>
         <v/>
       </c>
-      <c r="F27" s="313" t="n">
+      <c r="F27" s="315" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="265">
@@ -3470,26 +3470,26 @@
       <c r="I27" s="274" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A28" s="303" t="inlineStr">
+      <c r="A28" s="310" t="inlineStr">
         <is>
           <t>Aquamarine AB</t>
         </is>
       </c>
-      <c r="B28" s="303" t="inlineStr">
+      <c r="B28" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C28" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D28" s="303" t="n">
+      <c r="C28" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D28" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E28" s="303" t="n">
+      <c r="E28" s="310" t="n">
         <v>50</v>
       </c>
-      <c r="F28" s="311">
+      <c r="F28" s="313">
         <f>1+1+1+1+1</f>
         <v/>
       </c>
@@ -3510,21 +3510,21 @@
     </row>
     <row r="29">
       <c r="A29" s="429" t="n"/>
-      <c r="B29" s="301" t="inlineStr">
+      <c r="B29" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C29" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D29" s="301" t="n">
+      <c r="C29" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D29" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E29" s="301" t="n">
+      <c r="E29" s="311" t="n">
         <v>40</v>
       </c>
-      <c r="F29" s="312">
+      <c r="F29" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="30">
       <c r="A30" s="429" t="n"/>
-      <c r="B30" s="301" t="inlineStr">
+      <c r="B30" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C30" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D30" s="301" t="n">
+      <c r="C30" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D30" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E30" s="301">
+      <c r="E30" s="311">
         <f>15+35</f>
         <v/>
       </c>
-      <c r="F30" s="312" t="n">
+      <c r="F30" s="314" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="264">
@@ -3572,22 +3572,22 @@
     </row>
     <row r="31">
       <c r="A31" s="429" t="n"/>
-      <c r="B31" s="301" t="inlineStr">
+      <c r="B31" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C31" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D31" s="301" t="n">
+      <c r="C31" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D31" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E31" s="301">
+      <c r="E31" s="311">
         <f>30+19</f>
         <v/>
       </c>
-      <c r="F31" s="312">
+      <c r="F31" s="314">
         <f>1+1+1+1</f>
         <v/>
       </c>
@@ -3604,22 +3604,22 @@
     </row>
     <row r="32">
       <c r="A32" s="429" t="n"/>
-      <c r="B32" s="301" t="inlineStr">
+      <c r="B32" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C32" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D32" s="301" t="n">
+      <c r="C32" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D32" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E32" s="301">
+      <c r="E32" s="311">
         <f>23+25</f>
         <v/>
       </c>
-      <c r="F32" s="312">
+      <c r="F32" s="314">
         <f>1+1+1+1+1+1+1+1+1+1</f>
         <v/>
       </c>
@@ -3636,22 +3636,22 @@
     </row>
     <row r="33">
       <c r="A33" s="429" t="n"/>
-      <c r="B33" s="301" t="inlineStr">
+      <c r="B33" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C33" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D33" s="301" t="n">
+      <c r="C33" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D33" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E33" s="301">
+      <c r="E33" s="311">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F33" s="312">
+      <c r="F33" s="314">
         <f>6+3+1+2+1+1</f>
         <v/>
       </c>
@@ -3668,22 +3668,22 @@
     </row>
     <row r="34">
       <c r="A34" s="429" t="n"/>
-      <c r="B34" s="301" t="inlineStr">
+      <c r="B34" s="311" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C34" s="301" t="n">
+      <c r="C34" s="311" t="n">
         <v>288</v>
       </c>
-      <c r="D34" s="301" t="n">
+      <c r="D34" s="311" t="n">
         <v>478</v>
       </c>
-      <c r="E34" s="301">
+      <c r="E34" s="311">
         <f>24+25</f>
         <v/>
       </c>
-      <c r="F34" s="312">
+      <c r="F34" s="314">
         <f>1+2+1+1</f>
         <v/>
       </c>
@@ -3700,22 +3700,22 @@
     </row>
     <row r="35" ht="15.75" customHeight="1" thickBot="1">
       <c r="A35" s="431" t="n"/>
-      <c r="B35" s="339" t="inlineStr">
+      <c r="B35" s="331" t="inlineStr">
         <is>
           <t>SS34</t>
         </is>
       </c>
-      <c r="C35" s="302" t="n">
+      <c r="C35" s="312" t="n">
         <v>144</v>
       </c>
-      <c r="D35" s="302" t="n">
+      <c r="D35" s="312" t="n">
         <v>800</v>
       </c>
-      <c r="E35" s="302">
+      <c r="E35" s="312">
         <f>3*25+23</f>
         <v/>
       </c>
-      <c r="F35" s="313" t="n"/>
+      <c r="F35" s="315" t="n"/>
       <c r="G35" s="265">
         <f>E35-F35</f>
         <v/>
@@ -3728,26 +3728,26 @@
       <c r="I35" s="274" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A36" s="303" t="inlineStr">
+      <c r="A36" s="310" t="inlineStr">
         <is>
           <t>Capri Blue AB</t>
         </is>
       </c>
-      <c r="B36" s="303" t="inlineStr">
+      <c r="B36" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C36" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D36" s="303" t="n">
+      <c r="C36" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D36" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E36" s="303" t="n">
+      <c r="E36" s="310" t="n">
         <v>48</v>
       </c>
-      <c r="F36" s="311" t="n"/>
+      <c r="F36" s="313" t="n"/>
       <c r="G36" s="263">
         <f>E36-F36</f>
         <v/>
@@ -3765,21 +3765,21 @@
     </row>
     <row r="37">
       <c r="A37" s="429" t="n"/>
-      <c r="B37" s="301" t="inlineStr">
+      <c r="B37" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C37" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D37" s="301" t="n">
+      <c r="C37" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D37" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E37" s="301" t="n">
+      <c r="E37" s="311" t="n">
         <v>40</v>
       </c>
-      <c r="F37" s="312" t="n"/>
+      <c r="F37" s="314" t="n"/>
       <c r="G37" s="264">
         <f>E37-F37</f>
         <v/>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="38">
       <c r="A38" s="429" t="n"/>
-      <c r="B38" s="301" t="inlineStr">
+      <c r="B38" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C38" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D38" s="301" t="n">
+      <c r="C38" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D38" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E38" s="301">
+      <c r="E38" s="311">
         <f>14+35</f>
         <v/>
       </c>
-      <c r="F38" s="312" t="n"/>
+      <c r="F38" s="314" t="n"/>
       <c r="G38" s="264">
         <f>E38-F38</f>
         <v/>
@@ -3822,22 +3822,22 @@
     </row>
     <row r="39">
       <c r="A39" s="429" t="n"/>
-      <c r="B39" s="301" t="inlineStr">
+      <c r="B39" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C39" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D39" s="301" t="n">
+      <c r="C39" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D39" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E39" s="301">
+      <c r="E39" s="311">
         <f>19+30</f>
         <v/>
       </c>
-      <c r="F39" s="312" t="n"/>
+      <c r="F39" s="314" t="n"/>
       <c r="G39" s="264">
         <f>E39-F39</f>
         <v/>
@@ -3851,22 +3851,22 @@
     </row>
     <row r="40">
       <c r="A40" s="429" t="n"/>
-      <c r="B40" s="301" t="inlineStr">
+      <c r="B40" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C40" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D40" s="301" t="n">
+      <c r="C40" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D40" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E40" s="301">
+      <c r="E40" s="311">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F40" s="312">
+      <c r="F40" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -3883,22 +3883,22 @@
     </row>
     <row r="41">
       <c r="A41" s="429" t="n"/>
-      <c r="B41" s="301" t="inlineStr">
+      <c r="B41" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C41" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D41" s="301" t="n">
+      <c r="C41" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D41" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E41" s="301">
+      <c r="E41" s="311">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F41" s="312">
+      <c r="F41" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="42" ht="15.75" customHeight="1" thickBot="1">
       <c r="A42" s="431" t="n"/>
-      <c r="B42" s="302" t="inlineStr">
+      <c r="B42" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C42" s="302" t="n">
+      <c r="C42" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D42" s="302" t="n">
+      <c r="D42" s="312" t="n">
         <v>478</v>
       </c>
-      <c r="E42" s="302">
+      <c r="E42" s="312">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F42" s="313" t="n">
+      <c r="F42" s="315" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="265">
@@ -3945,26 +3945,26 @@
       <c r="I42" s="274" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A43" s="338" t="inlineStr">
+      <c r="A43" s="329" t="inlineStr">
         <is>
           <t>Montana AB</t>
         </is>
       </c>
-      <c r="B43" s="303" t="inlineStr">
+      <c r="B43" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C43" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D43" s="303" t="n">
+      <c r="C43" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D43" s="310" t="n">
         <v>150</v>
       </c>
-      <c r="E43" s="303" t="n">
+      <c r="E43" s="310" t="n">
         <v>49</v>
       </c>
-      <c r="F43" s="311" t="n"/>
+      <c r="F43" s="313" t="n"/>
       <c r="G43" s="263">
         <f>E43-F43</f>
         <v/>
@@ -3982,21 +3982,21 @@
     </row>
     <row r="44" ht="15.75" customHeight="1" thickBot="1">
       <c r="A44" s="429" t="n"/>
-      <c r="B44" s="301" t="inlineStr">
+      <c r="B44" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C44" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D44" s="301" t="n">
+      <c r="C44" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D44" s="311" t="n">
         <v>190</v>
       </c>
-      <c r="E44" s="301" t="n">
+      <c r="E44" s="311" t="n">
         <v>40</v>
       </c>
-      <c r="F44" s="312" t="n"/>
+      <c r="F44" s="314" t="n"/>
       <c r="G44" s="264">
         <f>E44-F44</f>
         <v/>
@@ -4010,21 +4010,21 @@
     </row>
     <row r="45" ht="15.75" customHeight="1" thickBot="1">
       <c r="A45" s="429" t="n"/>
-      <c r="B45" s="301" t="inlineStr">
+      <c r="B45" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C45" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D45" s="301" t="n">
+      <c r="C45" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D45" s="311" t="n">
         <v>210</v>
       </c>
-      <c r="E45" s="301" t="n">
+      <c r="E45" s="311" t="n">
         <v>35</v>
       </c>
-      <c r="F45" s="312" t="n"/>
+      <c r="F45" s="314" t="n"/>
       <c r="G45" s="264">
         <f>E45-F45</f>
         <v/>
@@ -4038,22 +4038,22 @@
     </row>
     <row r="46">
       <c r="A46" s="429" t="n"/>
-      <c r="B46" s="301" t="inlineStr">
+      <c r="B46" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C46" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D46" s="301" t="n">
+      <c r="C46" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D46" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E46" s="301">
+      <c r="E46" s="311">
         <f>10+30+6</f>
         <v/>
       </c>
-      <c r="F46" s="312" t="n">
+      <c r="F46" s="314" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="264">
@@ -4069,22 +4069,22 @@
     </row>
     <row r="47">
       <c r="A47" s="429" t="n"/>
-      <c r="B47" s="301" t="inlineStr">
+      <c r="B47" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C47" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D47" s="301" t="n">
+      <c r="C47" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D47" s="311" t="n">
         <v>415</v>
       </c>
-      <c r="E47" s="301">
+      <c r="E47" s="311">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F47" s="312" t="n"/>
+      <c r="F47" s="314" t="n"/>
       <c r="G47" s="264">
         <f>E47-F47</f>
         <v/>
@@ -4098,22 +4098,22 @@
     </row>
     <row r="48">
       <c r="A48" s="429" t="n"/>
-      <c r="B48" s="301" t="inlineStr">
+      <c r="B48" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C48" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D48" s="301" t="n">
+      <c r="C48" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D48" s="311" t="n">
         <v>715</v>
       </c>
-      <c r="E48" s="301">
+      <c r="E48" s="311">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F48" s="312" t="n"/>
+      <c r="F48" s="314" t="n"/>
       <c r="G48" s="264">
         <f>E48-F48</f>
         <v/>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="49">
       <c r="A49" s="429" t="n"/>
-      <c r="B49" s="301" t="inlineStr">
+      <c r="B49" s="311" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C49" s="301" t="n">
+      <c r="C49" s="311" t="n">
         <v>288</v>
       </c>
-      <c r="D49" s="301" t="n">
+      <c r="D49" s="311" t="n">
         <v>415</v>
       </c>
-      <c r="E49" s="301">
+      <c r="E49" s="311">
         <f>22+25</f>
         <v/>
       </c>
-      <c r="F49" s="312" t="n"/>
+      <c r="F49" s="314" t="n"/>
       <c r="G49" s="264">
         <f>E49-F49</f>
         <v/>
@@ -4156,22 +4156,22 @@
     </row>
     <row r="50" ht="15.75" customHeight="1" thickBot="1">
       <c r="A50" s="431" t="n"/>
-      <c r="B50" s="339" t="inlineStr">
+      <c r="B50" s="331" t="inlineStr">
         <is>
           <t>SS34</t>
         </is>
       </c>
-      <c r="C50" s="302" t="n">
+      <c r="C50" s="312" t="n">
         <v>144</v>
       </c>
-      <c r="D50" s="302" t="n">
+      <c r="D50" s="312" t="n">
         <v>800</v>
       </c>
-      <c r="E50" s="302">
+      <c r="E50" s="312">
         <f>21+3*25</f>
         <v/>
       </c>
-      <c r="F50" s="313" t="n"/>
+      <c r="F50" s="315" t="n"/>
       <c r="G50" s="265">
         <f>E50-F50</f>
         <v/>
@@ -4184,26 +4184,26 @@
       <c r="I50" s="274" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A51" s="303" t="inlineStr">
+      <c r="A51" s="310" t="inlineStr">
         <is>
           <t>Lt. Peridot AB</t>
         </is>
       </c>
-      <c r="B51" s="338" t="inlineStr">
+      <c r="B51" s="329" t="inlineStr">
         <is>
           <t>SS3</t>
         </is>
       </c>
-      <c r="C51" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D51" s="303" t="n">
+      <c r="C51" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D51" s="310" t="n">
         <v>210</v>
       </c>
-      <c r="E51" s="303" t="n">
+      <c r="E51" s="310" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="311" t="n"/>
+      <c r="F51" s="313" t="n"/>
       <c r="G51" s="263">
         <f>E51-F51</f>
         <v/>
@@ -4221,21 +4221,21 @@
     </row>
     <row r="52">
       <c r="A52" s="429" t="n"/>
-      <c r="B52" s="336" t="inlineStr">
+      <c r="B52" s="330" t="inlineStr">
         <is>
           <t>SS4</t>
         </is>
       </c>
-      <c r="C52" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D52" s="301" t="n">
+      <c r="C52" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D52" s="311" t="n">
         <v>210</v>
       </c>
-      <c r="E52" s="301" t="n">
+      <c r="E52" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F52" s="312" t="n"/>
+      <c r="F52" s="314" t="n"/>
       <c r="G52" s="264">
         <f>E52-F52</f>
         <v/>
@@ -4249,21 +4249,21 @@
     </row>
     <row r="53">
       <c r="A53" s="429" t="n"/>
-      <c r="B53" s="301" t="inlineStr">
+      <c r="B53" s="311" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C53" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D53" s="301" t="n">
+      <c r="C53" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D53" s="311" t="n">
         <v>221</v>
       </c>
-      <c r="E53" s="301" t="n">
+      <c r="E53" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F53" s="312" t="n">
+      <c r="F53" s="314" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="264">
@@ -4279,21 +4279,21 @@
     </row>
     <row r="54">
       <c r="A54" s="429" t="n"/>
-      <c r="B54" s="301" t="inlineStr">
+      <c r="B54" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C54" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D54" s="301" t="n">
+      <c r="C54" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D54" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E54" s="301" t="n">
+      <c r="E54" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F54" s="312" t="n"/>
+      <c r="F54" s="314" t="n"/>
       <c r="G54" s="264">
         <f>E54-F54</f>
         <v/>
@@ -4307,21 +4307,21 @@
     </row>
     <row r="55">
       <c r="A55" s="429" t="n"/>
-      <c r="B55" s="301" t="inlineStr">
+      <c r="B55" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C55" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D55" s="301" t="n">
+      <c r="C55" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D55" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E55" s="301" t="n">
+      <c r="E55" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F55" s="312" t="n">
+      <c r="F55" s="314" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="264">
@@ -4337,21 +4337,21 @@
     </row>
     <row r="56">
       <c r="A56" s="429" t="n"/>
-      <c r="B56" s="301" t="inlineStr">
+      <c r="B56" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C56" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D56" s="301" t="n">
+      <c r="C56" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D56" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E56" s="301" t="n">
+      <c r="E56" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F56" s="312">
+      <c r="F56" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -4368,21 +4368,21 @@
     </row>
     <row r="57">
       <c r="A57" s="429" t="n"/>
-      <c r="B57" s="301" t="inlineStr">
+      <c r="B57" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C57" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D57" s="301" t="n">
+      <c r="C57" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D57" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E57" s="301" t="n">
+      <c r="E57" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F57" s="312">
+      <c r="F57" s="314">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -4399,21 +4399,21 @@
     </row>
     <row r="58">
       <c r="A58" s="429" t="n"/>
-      <c r="B58" s="301" t="inlineStr">
+      <c r="B58" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C58" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D58" s="301" t="n">
+      <c r="C58" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D58" s="311" t="n">
         <v>802</v>
       </c>
-      <c r="E58" s="301" t="n">
+      <c r="E58" s="311" t="n">
         <v>3</v>
       </c>
-      <c r="F58" s="312">
+      <c r="F58" s="314">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -4430,21 +4430,21 @@
     </row>
     <row r="59" ht="15.75" customHeight="1" thickBot="1">
       <c r="A59" s="431" t="n"/>
-      <c r="B59" s="302" t="inlineStr">
+      <c r="B59" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C59" s="302" t="n">
+      <c r="C59" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D59" s="302" t="n">
+      <c r="D59" s="312" t="n">
         <v>470</v>
       </c>
-      <c r="E59" s="302" t="n">
+      <c r="E59" s="312" t="n">
         <v>5</v>
       </c>
-      <c r="F59" s="313">
+      <c r="F59" s="315">
         <f>3+1</f>
         <v/>
       </c>
@@ -4465,22 +4465,22 @@
           <t xml:space="preserve">Emerald AB </t>
         </is>
       </c>
-      <c r="B60" s="303" t="inlineStr">
+      <c r="B60" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C60" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D60" s="303" t="n">
+      <c r="C60" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D60" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E60" s="303">
+      <c r="E60" s="310">
         <f>1+54</f>
         <v/>
       </c>
-      <c r="F60" s="303">
+      <c r="F60" s="310">
         <f>1+1</f>
         <v/>
       </c>
@@ -4493,7 +4493,7 @@
           <t>12cut/Emerald AB/SS6/Non/026+</t>
         </is>
       </c>
-      <c r="I60" s="376" t="inlineStr">
+      <c r="I60" s="379" t="inlineStr">
         <is>
           <t>026+</t>
         </is>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="61">
       <c r="A61" s="429" t="n"/>
-      <c r="B61" s="301" t="inlineStr">
+      <c r="B61" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C61" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D61" s="301" t="n">
+      <c r="C61" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D61" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E61" s="301">
+      <c r="E61" s="311">
         <f>1+45</f>
         <v/>
       </c>
-      <c r="F61" s="301" t="n"/>
+      <c r="F61" s="311" t="n"/>
       <c r="G61" s="245">
         <f>E61-F61</f>
         <v/>
@@ -4530,22 +4530,22 @@
     </row>
     <row r="62">
       <c r="A62" s="429" t="n"/>
-      <c r="B62" s="301" t="inlineStr">
+      <c r="B62" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C62" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D62" s="301" t="n">
+      <c r="C62" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D62" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E62" s="301">
+      <c r="E62" s="311">
         <f>52+2</f>
         <v/>
       </c>
-      <c r="F62" s="301" t="n"/>
+      <c r="F62" s="311" t="n"/>
       <c r="G62" s="245">
         <f>E62-F62</f>
         <v/>
@@ -4559,22 +4559,22 @@
     </row>
     <row r="63">
       <c r="A63" s="429" t="n"/>
-      <c r="B63" s="301" t="inlineStr">
+      <c r="B63" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C63" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D63" s="301" t="n">
+      <c r="C63" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D63" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E63" s="301">
+      <c r="E63" s="311">
         <f>50+2</f>
         <v/>
       </c>
-      <c r="F63" s="301" t="n">
+      <c r="F63" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="245">
@@ -4590,22 +4590,22 @@
     </row>
     <row r="64">
       <c r="A64" s="429" t="n"/>
-      <c r="B64" s="301" t="inlineStr">
+      <c r="B64" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C64" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D64" s="301" t="n">
+      <c r="C64" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D64" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E64" s="301">
+      <c r="E64" s="311">
         <f>25+23+1</f>
         <v/>
       </c>
-      <c r="F64" s="318">
+      <c r="F64" s="320">
         <f>1+1</f>
         <v/>
       </c>
@@ -4622,22 +4622,22 @@
     </row>
     <row r="65">
       <c r="A65" s="429" t="n"/>
-      <c r="B65" s="301" t="inlineStr">
+      <c r="B65" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C65" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D65" s="301" t="n">
+      <c r="C65" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D65" s="311" t="n">
         <v>802</v>
       </c>
-      <c r="E65" s="301">
+      <c r="E65" s="311">
         <f>3*15+2</f>
         <v/>
       </c>
-      <c r="F65" s="318">
+      <c r="F65" s="320">
         <f>1+1+1+1</f>
         <v/>
       </c>
@@ -4654,22 +4654,22 @@
     </row>
     <row r="66" ht="15.75" customHeight="1" thickBot="1">
       <c r="A66" s="433" t="n"/>
-      <c r="B66" s="302" t="inlineStr">
+      <c r="B66" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C66" s="302" t="n">
+      <c r="C66" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D66" s="302" t="n">
+      <c r="D66" s="312" t="n">
         <v>470</v>
       </c>
-      <c r="E66" s="302">
+      <c r="E66" s="312">
         <f>1+50</f>
         <v/>
       </c>
-      <c r="F66" s="302">
+      <c r="F66" s="312">
         <f>1+1</f>
         <v/>
       </c>
@@ -4685,26 +4685,26 @@
       <c r="I66" s="430" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A67" s="303" t="inlineStr">
+      <c r="A67" s="310" t="inlineStr">
         <is>
           <t xml:space="preserve">Lt. Peach AB </t>
         </is>
       </c>
-      <c r="B67" s="303" t="inlineStr">
+      <c r="B67" s="310" t="inlineStr">
         <is>
           <t>SS3</t>
         </is>
       </c>
-      <c r="C67" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D67" s="303" t="n">
+      <c r="C67" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D67" s="310" t="n">
         <v>258</v>
       </c>
-      <c r="E67" s="303" t="n">
+      <c r="E67" s="310" t="n">
         <v>5</v>
       </c>
-      <c r="F67" s="303" t="n"/>
+      <c r="F67" s="310" t="n"/>
       <c r="G67" s="243">
         <f>E67-F67</f>
         <v/>
@@ -4722,22 +4722,22 @@
     </row>
     <row r="68">
       <c r="A68" s="429" t="n"/>
-      <c r="B68" s="301" t="inlineStr">
+      <c r="B68" s="311" t="inlineStr">
         <is>
           <t>SS4</t>
         </is>
       </c>
-      <c r="C68" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D68" s="301" t="n">
+      <c r="C68" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D68" s="311" t="n">
         <v>258</v>
       </c>
-      <c r="E68" s="301">
+      <c r="E68" s="311">
         <f>1+4</f>
         <v/>
       </c>
-      <c r="F68" s="301" t="n">
+      <c r="F68" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="245">
@@ -4753,22 +4753,22 @@
     </row>
     <row r="69">
       <c r="A69" s="429" t="n"/>
-      <c r="B69" s="301" t="inlineStr">
+      <c r="B69" s="311" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C69" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D69" s="301" t="n">
+      <c r="C69" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D69" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E69" s="301">
+      <c r="E69" s="311">
         <f>1+4</f>
         <v/>
       </c>
-      <c r="F69" s="301" t="n"/>
+      <c r="F69" s="311" t="n"/>
       <c r="G69" s="245">
         <f>E69-F69</f>
         <v/>
@@ -4782,22 +4782,22 @@
     </row>
     <row r="70">
       <c r="A70" s="429" t="n"/>
-      <c r="B70" s="301" t="inlineStr">
+      <c r="B70" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C70" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D70" s="301" t="n">
+      <c r="C70" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D70" s="311" t="n">
         <v>325</v>
       </c>
-      <c r="E70" s="301">
+      <c r="E70" s="311">
         <f>1+4</f>
         <v/>
       </c>
-      <c r="F70" s="301" t="n">
+      <c r="F70" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="245">
@@ -4813,22 +4813,22 @@
     </row>
     <row r="71">
       <c r="A71" s="429" t="n"/>
-      <c r="B71" s="301" t="inlineStr">
+      <c r="B71" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C71" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D71" s="301" t="n">
+      <c r="C71" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D71" s="311" t="n">
         <v>359</v>
       </c>
-      <c r="E71" s="301">
+      <c r="E71" s="311">
         <f>1+7</f>
         <v/>
       </c>
-      <c r="F71" s="301" t="n"/>
+      <c r="F71" s="311" t="n"/>
       <c r="G71" s="245">
         <f>E71-F71</f>
         <v/>
@@ -4842,22 +4842,22 @@
     </row>
     <row r="72">
       <c r="A72" s="429" t="n"/>
-      <c r="B72" s="301" t="inlineStr">
+      <c r="B72" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C72" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D72" s="301" t="n">
+      <c r="C72" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D72" s="311" t="n">
         <v>513</v>
       </c>
-      <c r="E72" s="301">
+      <c r="E72" s="311">
         <f>1+7</f>
         <v/>
       </c>
-      <c r="F72" s="301">
+      <c r="F72" s="311">
         <f>1+1</f>
         <v/>
       </c>
@@ -4874,22 +4874,22 @@
     </row>
     <row r="73">
       <c r="A73" s="429" t="n"/>
-      <c r="B73" s="301" t="inlineStr">
+      <c r="B73" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C73" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D73" s="301" t="n">
+      <c r="C73" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D73" s="311" t="n">
         <v>720</v>
       </c>
-      <c r="E73" s="301">
+      <c r="E73" s="311">
         <f>1+4</f>
         <v/>
       </c>
-      <c r="F73" s="301">
+      <c r="F73" s="311">
         <f>1+1</f>
         <v/>
       </c>
@@ -4906,21 +4906,21 @@
     </row>
     <row r="74">
       <c r="A74" s="429" t="n"/>
-      <c r="B74" s="301" t="inlineStr">
+      <c r="B74" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C74" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D74" s="301" t="n">
+      <c r="C74" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D74" s="311" t="n">
         <v>1051</v>
       </c>
-      <c r="E74" s="301" t="n">
+      <c r="E74" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="301" t="n">
+      <c r="F74" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="245">
@@ -4936,21 +4936,21 @@
     </row>
     <row r="75" ht="15.75" customHeight="1" thickBot="1">
       <c r="A75" s="431" t="n"/>
-      <c r="B75" s="302" t="inlineStr">
+      <c r="B75" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C75" s="302" t="n">
+      <c r="C75" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D75" s="302" t="n">
+      <c r="D75" s="312" t="n">
         <v>691</v>
       </c>
-      <c r="E75" s="302" t="n">
+      <c r="E75" s="312" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="302" t="n">
+      <c r="F75" s="312" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="246">
@@ -4965,27 +4965,27 @@
       <c r="I75" s="274" t="n"/>
     </row>
     <row r="76" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A76" s="303" t="inlineStr">
+      <c r="A76" s="310" t="inlineStr">
         <is>
           <t>Hyacinth AB</t>
         </is>
       </c>
-      <c r="B76" s="303" t="inlineStr">
+      <c r="B76" s="310" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C76" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D76" s="303" t="n">
+      <c r="C76" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D76" s="310" t="n">
         <v>286</v>
       </c>
-      <c r="E76" s="303">
+      <c r="E76" s="310">
         <f>40+10</f>
         <v/>
       </c>
-      <c r="F76" s="303" t="n"/>
+      <c r="F76" s="310" t="n"/>
       <c r="G76" s="243">
         <f>E76-F76</f>
         <v/>
@@ -5003,22 +5003,22 @@
     </row>
     <row r="77" ht="15.75" customHeight="1" thickBot="1">
       <c r="A77" s="429" t="n"/>
-      <c r="B77" s="301" t="inlineStr">
+      <c r="B77" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C77" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D77" s="301" t="n">
+      <c r="C77" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D77" s="311" t="n">
         <v>455</v>
       </c>
-      <c r="E77" s="301">
+      <c r="E77" s="311">
         <f>20+30</f>
         <v/>
       </c>
-      <c r="F77" s="301" t="n"/>
+      <c r="F77" s="311" t="n"/>
       <c r="G77" s="245">
         <f>E77-F77</f>
         <v/>
@@ -5032,22 +5032,22 @@
     </row>
     <row r="78">
       <c r="A78" s="429" t="n"/>
-      <c r="B78" s="301" t="inlineStr">
+      <c r="B78" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C78" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D78" s="301" t="n">
+      <c r="C78" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D78" s="311" t="n">
         <v>565</v>
       </c>
-      <c r="E78" s="301">
+      <c r="E78" s="311">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F78" s="301">
+      <c r="F78" s="311">
         <f>2+2+1+1</f>
         <v/>
       </c>
@@ -5064,22 +5064,22 @@
     </row>
     <row r="79">
       <c r="A79" s="429" t="n"/>
-      <c r="B79" s="301" t="inlineStr">
+      <c r="B79" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C79" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D79" s="301" t="n">
+      <c r="C79" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D79" s="311" t="n">
         <v>893</v>
       </c>
-      <c r="E79" s="301">
+      <c r="E79" s="311">
         <f>3*15+5</f>
         <v/>
       </c>
-      <c r="F79" s="301">
+      <c r="F79" s="311">
         <f>6+2+1</f>
         <v/>
       </c>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="80" ht="15.75" customHeight="1" thickBot="1">
       <c r="A80" s="431" t="n"/>
-      <c r="B80" s="302" t="inlineStr">
+      <c r="B80" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C80" s="302" t="n">
+      <c r="C80" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D80" s="302" t="n">
+      <c r="D80" s="312" t="n">
         <v>610</v>
       </c>
-      <c r="E80" s="302">
+      <c r="E80" s="312">
         <f>23+25</f>
         <v/>
       </c>
-      <c r="F80" s="302">
+      <c r="F80" s="312">
         <f>1+1</f>
         <v/>
       </c>
@@ -5127,27 +5127,27 @@
       <c r="I80" s="274" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A81" s="303" t="inlineStr">
+      <c r="A81" s="310" t="inlineStr">
         <is>
           <t>Citrine AB</t>
         </is>
       </c>
-      <c r="B81" s="303" t="inlineStr">
+      <c r="B81" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C81" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D81" s="303" t="n">
+      <c r="C81" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D81" s="310" t="n">
         <v>246</v>
       </c>
-      <c r="E81" s="303">
+      <c r="E81" s="310">
         <f>50+5</f>
         <v/>
       </c>
-      <c r="F81" s="303">
+      <c r="F81" s="310">
         <f>1+1</f>
         <v/>
       </c>
@@ -5168,22 +5168,22 @@
     </row>
     <row r="82">
       <c r="A82" s="429" t="n"/>
-      <c r="B82" s="301" t="inlineStr">
+      <c r="B82" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C82" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D82" s="301" t="n">
+      <c r="C82" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D82" s="311" t="n">
         <v>286</v>
       </c>
-      <c r="E82" s="301">
+      <c r="E82" s="311">
         <f>40+5</f>
         <v/>
       </c>
-      <c r="F82" s="301" t="n">
+      <c r="F82" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="245">
@@ -5199,22 +5199,22 @@
     </row>
     <row r="83">
       <c r="A83" s="429" t="n"/>
-      <c r="B83" s="301" t="inlineStr">
+      <c r="B83" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C83" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D83" s="301" t="n">
+      <c r="C83" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D83" s="311" t="n">
         <v>315</v>
       </c>
-      <c r="E83" s="301">
+      <c r="E83" s="311">
         <f>50+5</f>
         <v/>
       </c>
-      <c r="F83" s="301" t="n"/>
+      <c r="F83" s="311" t="n"/>
       <c r="G83" s="245">
         <f>E83-F83</f>
         <v/>
@@ -5228,22 +5228,22 @@
     </row>
     <row r="84">
       <c r="A84" s="429" t="n"/>
-      <c r="B84" s="301" t="inlineStr">
+      <c r="B84" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C84" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D84" s="301" t="n">
+      <c r="C84" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D84" s="311" t="n">
         <v>455</v>
       </c>
-      <c r="E84" s="301">
+      <c r="E84" s="311">
         <f>50+5</f>
         <v/>
       </c>
-      <c r="F84" s="301" t="n"/>
+      <c r="F84" s="311" t="n"/>
       <c r="G84" s="245">
         <f>E84-F84</f>
         <v/>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="85">
       <c r="A85" s="429" t="n"/>
-      <c r="B85" s="301" t="inlineStr">
+      <c r="B85" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C85" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D85" s="301" t="n">
+      <c r="C85" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D85" s="311" t="n">
         <v>565</v>
       </c>
-      <c r="E85" s="301">
+      <c r="E85" s="311">
         <f>49+5</f>
         <v/>
       </c>
-      <c r="F85" s="301">
+      <c r="F85" s="311">
         <f>2+1+1</f>
         <v/>
       </c>
@@ -5289,22 +5289,22 @@
     </row>
     <row r="86">
       <c r="A86" s="429" t="n"/>
-      <c r="B86" s="301" t="inlineStr">
+      <c r="B86" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C86" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D86" s="301" t="n">
+      <c r="C86" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D86" s="311" t="n">
         <v>893</v>
       </c>
-      <c r="E86" s="301">
+      <c r="E86" s="311">
         <f>50+4</f>
         <v/>
       </c>
-      <c r="F86" s="301">
+      <c r="F86" s="311">
         <f>1+1+3+1+1</f>
         <v/>
       </c>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="87" ht="15.75" customHeight="1" thickBot="1">
       <c r="A87" s="431" t="n"/>
-      <c r="B87" s="302" t="inlineStr">
+      <c r="B87" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C87" s="302" t="n">
+      <c r="C87" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D87" s="302" t="n">
+      <c r="D87" s="312" t="n">
         <v>610</v>
       </c>
-      <c r="E87" s="302">
+      <c r="E87" s="312">
         <f>49+1</f>
         <v/>
       </c>
-      <c r="F87" s="302">
+      <c r="F87" s="312">
         <f>2+1+1+1</f>
         <v/>
       </c>
@@ -5352,7 +5352,7 @@
       <c r="I87" s="274" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A88" s="303" t="inlineStr">
+      <c r="A88" s="310" t="inlineStr">
         <is>
           <t xml:space="preserve">Lt.Rose AB </t>
         </is>
@@ -5362,16 +5362,16 @@
           <t>SS6</t>
         </is>
       </c>
-      <c r="C88" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D88" s="303" t="n">
+      <c r="C88" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D88" s="310" t="n">
         <v>385</v>
       </c>
-      <c r="E88" s="303" t="n">
+      <c r="E88" s="310" t="n">
         <v>50</v>
       </c>
-      <c r="F88" s="303">
+      <c r="F88" s="310">
         <f>1+1</f>
         <v/>
       </c>
@@ -5392,22 +5392,22 @@
     </row>
     <row r="89">
       <c r="A89" s="429" t="n"/>
-      <c r="B89" s="301" t="inlineStr">
+      <c r="B89" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C89" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D89" s="301" t="n">
+      <c r="C89" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D89" s="311" t="n">
         <v>501</v>
       </c>
-      <c r="E89" s="301">
+      <c r="E89" s="311">
         <f>50+3</f>
         <v/>
       </c>
-      <c r="F89" s="301" t="n">
+      <c r="F89" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G89" s="245">
@@ -5423,22 +5423,22 @@
     </row>
     <row r="90">
       <c r="A90" s="429" t="n"/>
-      <c r="B90" s="301" t="inlineStr">
+      <c r="B90" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C90" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D90" s="301" t="n">
+      <c r="C90" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D90" s="311" t="n">
         <v>613</v>
       </c>
-      <c r="E90" s="301">
+      <c r="E90" s="311">
         <f>50+1</f>
         <v/>
       </c>
-      <c r="F90" s="301">
+      <c r="F90" s="311">
         <f>1+1</f>
         <v/>
       </c>
@@ -5455,22 +5455,22 @@
     </row>
     <row r="91">
       <c r="A91" s="429" t="n"/>
-      <c r="B91" s="301" t="inlineStr">
+      <c r="B91" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C91" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D91" s="301" t="n">
+      <c r="C91" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D91" s="311" t="n">
         <v>712</v>
       </c>
-      <c r="E91" s="336">
+      <c r="E91" s="330">
         <f>30+20</f>
         <v/>
       </c>
-      <c r="F91" s="301">
+      <c r="F91" s="311">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="92">
       <c r="A92" s="429" t="n"/>
-      <c r="B92" s="301" t="inlineStr">
+      <c r="B92" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C92" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D92" s="301" t="n">
+      <c r="C92" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D92" s="311" t="n">
         <v>1238</v>
       </c>
-      <c r="E92" s="301">
+      <c r="E92" s="311">
         <f>20+3</f>
         <v/>
       </c>
-      <c r="F92" s="301" t="n">
+      <c r="F92" s="311" t="n">
         <v>2</v>
       </c>
       <c r="G92" s="245">
@@ -5518,21 +5518,21 @@
     </row>
     <row r="93">
       <c r="A93" s="429" t="n"/>
-      <c r="B93" s="301" t="inlineStr">
+      <c r="B93" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C93" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D93" s="301" t="n">
+      <c r="C93" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D93" s="311" t="n">
         <v>2000</v>
       </c>
-      <c r="E93" s="301" t="n">
+      <c r="E93" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F93" s="301">
+      <c r="F93" s="311">
         <f>1+1</f>
         <v/>
       </c>
@@ -5549,22 +5549,22 @@
     </row>
     <row r="94" ht="15.75" customHeight="1" thickBot="1">
       <c r="A94" s="431" t="n"/>
-      <c r="B94" s="302" t="inlineStr">
+      <c r="B94" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C94" s="302" t="n">
+      <c r="C94" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D94" s="302" t="n">
+      <c r="D94" s="312" t="n">
         <v>1207</v>
       </c>
-      <c r="E94" s="302">
+      <c r="E94" s="312">
         <f>49+4+20</f>
         <v/>
       </c>
-      <c r="F94" s="302" t="n">
+      <c r="F94" s="312" t="n">
         <v>2</v>
       </c>
       <c r="G94" s="246">
@@ -5579,26 +5579,26 @@
       <c r="I94" s="274" t="n"/>
     </row>
     <row r="95" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A95" s="303" t="inlineStr">
+      <c r="A95" s="310" t="inlineStr">
         <is>
           <t xml:space="preserve">Lt. Siam Shimmer </t>
         </is>
       </c>
-      <c r="B95" s="338" t="inlineStr">
+      <c r="B95" s="329" t="inlineStr">
         <is>
           <t>SS3</t>
         </is>
       </c>
-      <c r="C95" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D95" s="303" t="n">
+      <c r="C95" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D95" s="310" t="n">
         <v>237</v>
       </c>
-      <c r="E95" s="303" t="n">
+      <c r="E95" s="310" t="n">
         <v>5</v>
       </c>
-      <c r="F95" s="303" t="n"/>
+      <c r="F95" s="310" t="n"/>
       <c r="G95" s="243">
         <f>E95-F95</f>
         <v/>
@@ -5616,21 +5616,21 @@
     </row>
     <row r="96">
       <c r="A96" s="429" t="n"/>
-      <c r="B96" s="336" t="inlineStr">
+      <c r="B96" s="330" t="inlineStr">
         <is>
           <t>SS4</t>
         </is>
       </c>
-      <c r="C96" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D96" s="301" t="n">
+      <c r="C96" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D96" s="311" t="n">
         <v>237</v>
       </c>
-      <c r="E96" s="301" t="n">
+      <c r="E96" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F96" s="301" t="n"/>
+      <c r="F96" s="311" t="n"/>
       <c r="G96" s="245">
         <f>E96-F96</f>
         <v/>
@@ -5644,21 +5644,21 @@
     </row>
     <row r="97">
       <c r="A97" s="429" t="n"/>
-      <c r="B97" s="301" t="inlineStr">
+      <c r="B97" s="311" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C97" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D97" s="301" t="n">
+      <c r="C97" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D97" s="311" t="n">
         <v>246</v>
       </c>
-      <c r="E97" s="301" t="n">
+      <c r="E97" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F97" s="301" t="n"/>
+      <c r="F97" s="311" t="n"/>
       <c r="G97" s="245">
         <f>E97-F97</f>
         <v/>
@@ -5672,21 +5672,21 @@
     </row>
     <row r="98">
       <c r="A98" s="429" t="n"/>
-      <c r="B98" s="301" t="inlineStr">
+      <c r="B98" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C98" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D98" s="301" t="n">
+      <c r="C98" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D98" s="311" t="n">
         <v>286</v>
       </c>
-      <c r="E98" s="301" t="n">
+      <c r="E98" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F98" s="301" t="n"/>
+      <c r="F98" s="311" t="n"/>
       <c r="G98" s="245">
         <f>E98-F98</f>
         <v/>
@@ -5700,21 +5700,21 @@
     </row>
     <row r="99">
       <c r="A99" s="429" t="n"/>
-      <c r="B99" s="301" t="inlineStr">
+      <c r="B99" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C99" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D99" s="301" t="n">
+      <c r="C99" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D99" s="311" t="n">
         <v>315</v>
       </c>
-      <c r="E99" s="301" t="n">
+      <c r="E99" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F99" s="301" t="n">
+      <c r="F99" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G99" s="245">
@@ -5730,21 +5730,21 @@
     </row>
     <row r="100">
       <c r="A100" s="429" t="n"/>
-      <c r="B100" s="301" t="inlineStr">
+      <c r="B100" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C100" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D100" s="301" t="n">
+      <c r="C100" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D100" s="311" t="n">
         <v>455</v>
       </c>
-      <c r="E100" s="301" t="n">
+      <c r="E100" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F100" s="301" t="n"/>
+      <c r="F100" s="311" t="n"/>
       <c r="G100" s="245">
         <f>E100-F100</f>
         <v/>
@@ -5758,21 +5758,21 @@
     </row>
     <row r="101">
       <c r="A101" s="429" t="n"/>
-      <c r="B101" s="301" t="inlineStr">
+      <c r="B101" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C101" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D101" s="301" t="n">
+      <c r="C101" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D101" s="311" t="n">
         <v>565</v>
       </c>
-      <c r="E101" s="301" t="n">
+      <c r="E101" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F101" s="301">
+      <c r="F101" s="311">
         <f>1+1+1+1</f>
         <v/>
       </c>
@@ -5789,22 +5789,22 @@
     </row>
     <row r="102">
       <c r="A102" s="429" t="n"/>
-      <c r="B102" s="301" t="inlineStr">
+      <c r="B102" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C102" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D102" s="301" t="n">
+      <c r="C102" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D102" s="311" t="n">
         <v>893</v>
       </c>
-      <c r="E102" s="301">
+      <c r="E102" s="311">
         <f>2+5</f>
         <v/>
       </c>
-      <c r="F102" s="301">
+      <c r="F102" s="311">
         <f>4+1+1</f>
         <v/>
       </c>
@@ -5821,21 +5821,21 @@
     </row>
     <row r="103" ht="15.75" customHeight="1" thickBot="1">
       <c r="A103" s="431" t="n"/>
-      <c r="B103" s="318" t="inlineStr">
+      <c r="B103" s="320" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C103" s="318" t="n">
+      <c r="C103" s="320" t="n">
         <v>288</v>
       </c>
-      <c r="D103" s="318" t="n">
+      <c r="D103" s="320" t="n">
         <v>610</v>
       </c>
-      <c r="E103" s="318" t="n">
+      <c r="E103" s="320" t="n">
         <v>5</v>
       </c>
-      <c r="F103" s="318" t="n">
+      <c r="F103" s="320" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="247">
@@ -5850,26 +5850,26 @@
       <c r="I103" s="274" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A104" s="303" t="inlineStr">
+      <c r="A104" s="310" t="inlineStr">
         <is>
           <t>Siam AB</t>
         </is>
       </c>
-      <c r="B104" s="303" t="inlineStr">
+      <c r="B104" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C104" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D104" s="303" t="n">
+      <c r="C104" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D104" s="310" t="n">
         <v>246</v>
       </c>
-      <c r="E104" s="303" t="n">
+      <c r="E104" s="310" t="n">
         <v>50</v>
       </c>
-      <c r="F104" s="303" t="n"/>
+      <c r="F104" s="310" t="n"/>
       <c r="G104" s="243">
         <f>E104-F104</f>
         <v/>
@@ -5887,22 +5887,22 @@
     </row>
     <row r="105">
       <c r="A105" s="429" t="n"/>
-      <c r="B105" s="301" t="inlineStr">
+      <c r="B105" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C105" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D105" s="301" t="n">
+      <c r="C105" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D105" s="311" t="n">
         <v>286</v>
       </c>
-      <c r="E105" s="301">
+      <c r="E105" s="311">
         <f>40+10</f>
         <v/>
       </c>
-      <c r="F105" s="301" t="n"/>
+      <c r="F105" s="311" t="n"/>
       <c r="G105" s="245">
         <f>E105-F105</f>
         <v/>
@@ -5916,22 +5916,22 @@
     </row>
     <row r="106">
       <c r="A106" s="429" t="n"/>
-      <c r="B106" s="301" t="inlineStr">
+      <c r="B106" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C106" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D106" s="301" t="n">
+      <c r="C106" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D106" s="311" t="n">
         <v>455</v>
       </c>
-      <c r="E106" s="301">
+      <c r="E106" s="311">
         <f>20+30</f>
         <v/>
       </c>
-      <c r="F106" s="301" t="n"/>
+      <c r="F106" s="311" t="n"/>
       <c r="G106" s="245">
         <f>E106-F106</f>
         <v/>
@@ -5945,22 +5945,22 @@
     </row>
     <row r="107">
       <c r="A107" s="429" t="n"/>
-      <c r="B107" s="301" t="inlineStr">
+      <c r="B107" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C107" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D107" s="301" t="n">
+      <c r="C107" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D107" s="311" t="n">
         <v>565</v>
       </c>
-      <c r="E107" s="301">
+      <c r="E107" s="311">
         <f>2*25</f>
         <v/>
       </c>
-      <c r="F107" s="301" t="n"/>
+      <c r="F107" s="311" t="n"/>
       <c r="G107" s="245">
         <f>E107-F107</f>
         <v/>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="108" ht="15.75" customHeight="1" thickBot="1">
       <c r="A108" s="431" t="n"/>
-      <c r="B108" s="302" t="inlineStr">
+      <c r="B108" s="312" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C108" s="302" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D108" s="302" t="n">
+      <c r="C108" s="312" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D108" s="312" t="n">
         <v>893</v>
       </c>
-      <c r="E108" s="302">
+      <c r="E108" s="312">
         <f>3*15</f>
         <v/>
       </c>
-      <c r="F108" s="302" t="n"/>
+      <c r="F108" s="312" t="n"/>
       <c r="G108" s="246">
         <f>E108-F108</f>
         <v/>
@@ -6002,26 +6002,26 @@
       <c r="I108" s="274" t="n"/>
     </row>
     <row r="109" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A109" s="317" t="inlineStr">
+      <c r="A109" s="319" t="inlineStr">
         <is>
           <t xml:space="preserve">Garnet AB </t>
         </is>
       </c>
-      <c r="B109" s="317" t="inlineStr">
+      <c r="B109" s="319" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C109" s="317" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D109" s="317" t="n">
+      <c r="C109" s="319" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D109" s="319" t="n">
         <v>246</v>
       </c>
-      <c r="E109" s="317" t="n">
+      <c r="E109" s="319" t="n">
         <v>5</v>
       </c>
-      <c r="F109" s="317" t="n"/>
+      <c r="F109" s="319" t="n"/>
       <c r="G109" s="244">
         <f>E109-F109</f>
         <v/>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="110">
       <c r="A110" s="429" t="n"/>
-      <c r="B110" s="301" t="inlineStr">
+      <c r="B110" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C110" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D110" s="301" t="n">
+      <c r="C110" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D110" s="311" t="n">
         <v>286</v>
       </c>
-      <c r="E110" s="301" t="n">
+      <c r="E110" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F110" s="301" t="n">
+      <c r="F110" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G110" s="245">
@@ -6069,21 +6069,21 @@
     </row>
     <row r="111">
       <c r="A111" s="429" t="n"/>
-      <c r="B111" s="301" t="inlineStr">
+      <c r="B111" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C111" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D111" s="301" t="n">
+      <c r="C111" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D111" s="311" t="n">
         <v>315</v>
       </c>
-      <c r="E111" s="301" t="n">
+      <c r="E111" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F111" s="301" t="n"/>
+      <c r="F111" s="311" t="n"/>
       <c r="G111" s="245">
         <f>E111-F111</f>
         <v/>
@@ -6097,21 +6097,21 @@
     </row>
     <row r="112">
       <c r="A112" s="429" t="n"/>
-      <c r="B112" s="301" t="inlineStr">
+      <c r="B112" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C112" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D112" s="301" t="n">
+      <c r="C112" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D112" s="311" t="n">
         <v>455</v>
       </c>
-      <c r="E112" s="301" t="n">
+      <c r="E112" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F112" s="301" t="n">
+      <c r="F112" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="245">
@@ -6127,21 +6127,21 @@
     </row>
     <row r="113">
       <c r="A113" s="429" t="n"/>
-      <c r="B113" s="301" t="inlineStr">
+      <c r="B113" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C113" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D113" s="301" t="n">
+      <c r="C113" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D113" s="311" t="n">
         <v>565</v>
       </c>
-      <c r="E113" s="301" t="n">
+      <c r="E113" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F113" s="301" t="n"/>
+      <c r="F113" s="311" t="n"/>
       <c r="G113" s="245">
         <f>E113-F113</f>
         <v/>
@@ -6155,21 +6155,21 @@
     </row>
     <row r="114">
       <c r="A114" s="429" t="n"/>
-      <c r="B114" s="301" t="inlineStr">
+      <c r="B114" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C114" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D114" s="301" t="n">
+      <c r="C114" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D114" s="311" t="n">
         <v>893</v>
       </c>
-      <c r="E114" s="301" t="n">
+      <c r="E114" s="311" t="n">
         <v>4</v>
       </c>
-      <c r="F114" s="301" t="n">
+      <c r="F114" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G114" s="245">
@@ -6185,21 +6185,21 @@
     </row>
     <row r="115" ht="15.75" customHeight="1" thickBot="1">
       <c r="A115" s="431" t="n"/>
-      <c r="B115" s="301" t="inlineStr">
+      <c r="B115" s="311" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C115" s="301" t="n">
+      <c r="C115" s="311" t="n">
         <v>288</v>
       </c>
-      <c r="D115" s="301" t="n">
+      <c r="D115" s="311" t="n">
         <v>610</v>
       </c>
-      <c r="E115" s="301" t="n">
+      <c r="E115" s="311" t="n">
         <v>4</v>
       </c>
-      <c r="F115" s="302" t="n"/>
+      <c r="F115" s="312" t="n"/>
       <c r="G115" s="246">
         <f>E115-F115</f>
         <v/>
@@ -6217,22 +6217,22 @@
           <t xml:space="preserve">Fuchsia AB </t>
         </is>
       </c>
-      <c r="B116" s="303" t="inlineStr">
+      <c r="B116" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C116" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D116" s="303" t="n">
+      <c r="C116" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D116" s="310" t="n">
         <v>369</v>
       </c>
-      <c r="E116" s="303">
+      <c r="E116" s="310">
         <f>2+3</f>
         <v/>
       </c>
-      <c r="F116" s="303" t="n"/>
+      <c r="F116" s="310" t="n"/>
       <c r="G116" s="243">
         <f>E116-F116</f>
         <v/>
@@ -6242,7 +6242,7 @@
           <t>12cut/Fuchsia Shimmer/SS6/Non/062</t>
         </is>
       </c>
-      <c r="I116" s="379" t="inlineStr">
+      <c r="I116" s="380" t="inlineStr">
         <is>
           <t>062</t>
         </is>
@@ -6250,22 +6250,22 @@
     </row>
     <row r="117">
       <c r="A117" s="429" t="n"/>
-      <c r="B117" s="301" t="inlineStr">
+      <c r="B117" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C117" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D117" s="301" t="n">
+      <c r="C117" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D117" s="311" t="n">
         <v>490</v>
       </c>
-      <c r="E117" s="301">
+      <c r="E117" s="311">
         <f>2+3</f>
         <v/>
       </c>
-      <c r="F117" s="301" t="n"/>
+      <c r="F117" s="311" t="n"/>
       <c r="G117" s="245">
         <f>E117-F117</f>
         <v/>
@@ -6279,22 +6279,22 @@
     </row>
     <row r="118">
       <c r="A118" s="429" t="n"/>
-      <c r="B118" s="301" t="inlineStr">
+      <c r="B118" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C118" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D118" s="301" t="n">
+      <c r="C118" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D118" s="311" t="n">
         <v>545</v>
       </c>
-      <c r="E118" s="301">
+      <c r="E118" s="311">
         <f>2+3</f>
         <v/>
       </c>
-      <c r="F118" s="301" t="n">
+      <c r="F118" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="245">
@@ -6310,22 +6310,22 @@
     </row>
     <row r="119">
       <c r="A119" s="429" t="n"/>
-      <c r="B119" s="301" t="inlineStr">
+      <c r="B119" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C119" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D119" s="301" t="n">
+      <c r="C119" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D119" s="311" t="n">
         <v>749</v>
       </c>
-      <c r="E119" s="301">
+      <c r="E119" s="311">
         <f>2+3</f>
         <v/>
       </c>
-      <c r="F119" s="301" t="n">
+      <c r="F119" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G119" s="245">
@@ -6341,22 +6341,22 @@
     </row>
     <row r="120">
       <c r="A120" s="429" t="n"/>
-      <c r="B120" s="301" t="inlineStr">
+      <c r="B120" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C120" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D120" s="301" t="n">
+      <c r="C120" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D120" s="311" t="n">
         <v>1013</v>
       </c>
-      <c r="E120" s="301">
+      <c r="E120" s="311">
         <f>2+3</f>
         <v/>
       </c>
-      <c r="F120" s="301" t="n">
+      <c r="F120" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G120" s="245">
@@ -6372,21 +6372,21 @@
     </row>
     <row r="121" ht="15.75" customHeight="1" thickBot="1">
       <c r="A121" s="429" t="n"/>
-      <c r="B121" s="301" t="inlineStr">
+      <c r="B121" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C121" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D121" s="301" t="n">
+      <c r="C121" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D121" s="311" t="n">
         <v>1513</v>
       </c>
-      <c r="E121" s="301" t="n">
+      <c r="E121" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F121" s="301">
+      <c r="F121" s="311">
         <f>1+1</f>
         <v/>
       </c>
@@ -6454,9 +6454,9 @@
     <mergeCell ref="A81:A87"/>
     <mergeCell ref="A13:A19"/>
     <mergeCell ref="A10:A12"/>
+    <mergeCell ref="I88:I94"/>
+    <mergeCell ref="I13:I19"/>
     <mergeCell ref="A109:A115"/>
-    <mergeCell ref="I13:I19"/>
-    <mergeCell ref="I88:I94"/>
     <mergeCell ref="I10:I12"/>
     <mergeCell ref="I60:I66"/>
     <mergeCell ref="I116:I121"/>
@@ -6474,8 +6474,8 @@
     <mergeCell ref="A67:A75"/>
     <mergeCell ref="A60:A66"/>
     <mergeCell ref="A51:A59"/>
+    <mergeCell ref="I76:I80"/>
     <mergeCell ref="A20:A27"/>
-    <mergeCell ref="I76:I80"/>
     <mergeCell ref="I95:I103"/>
     <mergeCell ref="I20:I27"/>
     <mergeCell ref="A28:A35"/>
